--- a/artfynd/A 29518-2025 artfynd.xlsx
+++ b/artfynd/A 29518-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266587</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266581</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266582</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266583</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266585</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266589</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266586</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266588</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266594</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266591</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266590</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,8 +2026,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266593</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29518-2025 artfynd.xlsx
+++ b/artfynd/A 29518-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135266587</v>
       </c>
       <c r="B2" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135266581</v>
       </c>
       <c r="B3" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135266582</v>
       </c>
       <c r="B4" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135266583</v>
       </c>
       <c r="B5" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135266585</v>
       </c>
       <c r="B6" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135266589</v>
       </c>
       <c r="B7" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135266586</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135266588</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135266594</v>
       </c>
       <c r="B10" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135266591</v>
       </c>
       <c r="B11" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135266590</v>
       </c>
       <c r="B12" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135266593</v>
       </c>
       <c r="B13" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29518-2025 artfynd.xlsx
+++ b/artfynd/A 29518-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135266587</v>
       </c>
       <c r="B2" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135266581</v>
       </c>
       <c r="B3" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135266582</v>
       </c>
       <c r="B4" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135266583</v>
       </c>
       <c r="B5" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135266585</v>
       </c>
       <c r="B6" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135266589</v>
       </c>
       <c r="B7" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135266586</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135266588</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135266594</v>
       </c>
       <c r="B10" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135266591</v>
       </c>
       <c r="B11" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135266590</v>
       </c>
       <c r="B12" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135266593</v>
       </c>
       <c r="B13" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29518-2025 artfynd.xlsx
+++ b/artfynd/A 29518-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135266587</v>
       </c>
       <c r="B2" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135266581</v>
       </c>
       <c r="B3" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135266582</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135266583</v>
       </c>
       <c r="B5" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135266585</v>
       </c>
       <c r="B6" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135266589</v>
       </c>
       <c r="B7" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
